--- a/docs/suivi-features.xlsx
+++ b/docs/suivi-features.xlsx
@@ -39,9 +39,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="0 %"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="0 %"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -153,10 +154,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,7 +168,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2925,11 +2926,13 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Cadrage</t>
         </is>
       </c>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="17" t="n"/>
+      <c r="H2" s="17" t="n">
+        <v>46285</v>
+      </c>
       <c r="I2" s="17" t="n"/>
       <c r="J2" s="17" t="n"/>
       <c r="K2" s="17" t="n"/>
@@ -2944,7 +2947,11 @@
         <f>IF(AND(M2&lt;&gt;"",O2&lt;&gt;""),O2-M2,"")</f>
         <v/>
       </c>
-      <c r="Q2" s="4" t="n"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>Fiche rédigée, 10 questions en attente</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">

--- a/docs/suivi-features.xlsx
+++ b/docs/suivi-features.xlsx
@@ -2933,7 +2933,9 @@
       <c r="H2" s="17" t="n">
         <v>46285</v>
       </c>
-      <c r="I2" s="17" t="n"/>
+      <c r="I2" s="17" t="n">
+        <v>46285</v>
+      </c>
       <c r="J2" s="17" t="n"/>
       <c r="K2" s="17" t="n"/>
       <c r="L2" s="17" t="n"/>
@@ -2949,7 +2951,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Fiche rédigée, 10 questions en attente</t>
+          <t>Étapes 1 et 2 closes ; étape 3 (plan) à faire</t>
         </is>
       </c>
     </row>

--- a/docs/suivi-features.xlsx
+++ b/docs/suivi-features.xlsx
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Cadrage</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="G2" s="4" t="n"/>
@@ -2936,7 +2936,9 @@
       <c r="I2" s="17" t="n">
         <v>46285</v>
       </c>
-      <c r="J2" s="17" t="n"/>
+      <c r="J2" s="17" t="n">
+        <v>46285</v>
+      </c>
       <c r="K2" s="17" t="n"/>
       <c r="L2" s="17" t="n"/>
       <c r="M2" s="17" t="n"/>
@@ -2951,7 +2953,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Étapes 1 et 2 closes ; étape 3 (plan) à faire</t>
+          <t>Plan validé ; étape 4 (tests d'abord) à faire</t>
         </is>
       </c>
     </row>

--- a/docs/suivi-features.xlsx
+++ b/docs/suivi-features.xlsx
@@ -39,10 +39,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0 %"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="0 %"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -144,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,10 +153,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +168,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -699,7 +700,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A6,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="18">
         <f>IF($D6=0,"",$I6/$D6)</f>
         <v/>
       </c>
@@ -747,7 +748,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A7,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="18">
         <f>IF($D7=0,"",$I7/$D7)</f>
         <v/>
       </c>
@@ -795,7 +796,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A8,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="18">
         <f>IF($D8=0,"",$I8/$D8)</f>
         <v/>
       </c>
@@ -843,7 +844,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A9,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="18">
         <f>IF($D9=0,"",$I9/$D9)</f>
         <v/>
       </c>
@@ -891,7 +892,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A10,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="18">
         <f>IF($D10=0,"",$I10/$D10)</f>
         <v/>
       </c>
@@ -939,7 +940,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A11,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="18">
         <f>IF($D11=0,"",$I11/$D11)</f>
         <v/>
       </c>
@@ -987,7 +988,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A12,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="18">
         <f>IF($D12=0,"",$I12/$D12)</f>
         <v/>
       </c>
@@ -1035,7 +1036,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A13,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="18">
         <f>IF($D13=0,"",$I13/$D13)</f>
         <v/>
       </c>
@@ -1083,7 +1084,7 @@
         <f>COUNTIFS(Features!$C$2:$C$74,$A14,Features!$F$2:$F$74,"Production")</f>
         <v/>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="18">
         <f>IF($D14=0,"",$I14/$D14)</f>
         <v/>
       </c>
@@ -1123,7 +1124,7 @@
         <f>SUM(I6:I14)</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="19">
         <f>IF($D15=0,"",$I15/$D15)</f>
         <v/>
       </c>
@@ -2926,21 +2927,39 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="17" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I2" s="17" t="n">
-        <v>46285</v>
-      </c>
-      <c r="J2" s="17" t="n">
-        <v>46285</v>
-      </c>
-      <c r="K2" s="17" t="n"/>
-      <c r="L2" s="17" t="n"/>
+          <t>In test</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="I2" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="K2" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="L2" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
       <c r="M2" s="17" t="n"/>
       <c r="N2" s="4">
         <f>IF(AND(H2&lt;&gt;"",M2&lt;&gt;""),M2-H2,"")</f>
